--- a/reportes/matriz_pruebas_proyecto.xlsx
+++ b/reportes/matriz_pruebas_proyecto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luis_\fitAppUSC\reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA480CD6-B924-4AA0-A1B9-B9160A73DC28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36670BAB-8896-4494-9AFF-8935CC9A78B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,7 +290,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,14 +302,9 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -353,13 +348,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -667,703 +661,702 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34" style="1" customWidth="1"/>
-    <col min="4" max="4" width="42" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="42" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="G2" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="G3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="G4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="2">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="G5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="G6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="G9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="G10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="G11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="G12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="G13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="G14" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="G15" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="G16" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
-        <v>1</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B17" s="2">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="G17" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="G18" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="2">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="G19" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
-        <v>1</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="G20" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
-        <v>1</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B21" s="2">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="G21" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="2">
         <v>50000</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="G22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="2">
         <v>50000</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="G23" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="2">
         <v>40000</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="G24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="2">
         <v>80000</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="G25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="2">
         <v>60000</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="2">
         <v>100000</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="G27" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="2">
         <v>60</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="G28" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="2">
         <v>60</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="G29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="2">
         <v>60</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>44</v>
       </c>
     </row>
